--- a/Collections/EURO/Netherlands/#EURO#Netherlands#Commemorative#[2007-present]#UNC.xlsx
+++ b/Collections/EURO/Netherlands/#EURO#Netherlands#Commemorative#[2007-present]#UNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Netherlands\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B4A939-2721-4EB5-A463-8A9274B00547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF68DC4-B9F0-4500-BA11-ED34039FE4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -80,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="62">
   <si>
     <t>Year</t>
   </si>
@@ -554,7 +557,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -721,9 +732,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -992,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="14" customWidth="1"/>
@@ -1880,6 +1891,39 @@
         <v/>
       </c>
     </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="J29" s="12" t="str">
+        <f t="shared" ref="J29" si="10">IF(OR(AND(I29&gt;1,I29&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:G2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
@@ -1887,12 +1931,12 @@
     <mergeCell ref="C1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="I3 I5 I7:I10 I12 I16">
-    <cfRule type="containsText" dxfId="19" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="47" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5 I3 I7:I10 I12 I16">
-    <cfRule type="colorScale" priority="46">
+  <conditionalFormatting sqref="I3 I5 I7:I10 I12 I16">
+    <cfRule type="colorScale" priority="48">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1904,11 +1948,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
+    <cfRule type="containsText" dxfId="19" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23 I25">
     <cfRule type="containsText" dxfId="18" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I22))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I23))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23 I25">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1920,13 +1981,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I23 I25">
-    <cfRule type="containsText" dxfId="17" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I23))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I25 I23">
-    <cfRule type="colorScale" priority="28">
+  <conditionalFormatting sqref="I4">
+    <cfRule type="containsText" dxfId="17" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -1937,12 +1998,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="containsText" dxfId="16" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
+  <conditionalFormatting sqref="I11">
+    <cfRule type="containsText" dxfId="16" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I11))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
+    <cfRule type="containsText" dxfId="15" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I6))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I6">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1954,12 +2032,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11">
-    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I11))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11">
+  <conditionalFormatting sqref="I20">
+    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I20))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
+    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I21))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
+    <cfRule type="containsText" dxfId="12" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1971,63 +2083,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I6))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I20))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
-    <cfRule type="containsText" dxfId="12" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I21))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
+  <conditionalFormatting sqref="I14">
     <cfRule type="containsText" dxfId="11" priority="19" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2039,12 +2100,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I14">
+  <conditionalFormatting sqref="I15">
     <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I14))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I14">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2056,12 +2117,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
+  <conditionalFormatting sqref="I17">
     <cfRule type="containsText" dxfId="9" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2073,12 +2134,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
+  <conditionalFormatting sqref="I18">
     <cfRule type="containsText" dxfId="8" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2090,12 +2151,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
+  <conditionalFormatting sqref="I19">
     <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2107,12 +2168,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I19">
+  <conditionalFormatting sqref="I24 I27">
     <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I19))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I19">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24 I27">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2124,13 +2185,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24 I27">
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I24))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I27 I24">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="I26">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I26">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2141,12 +2202,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26">
+  <conditionalFormatting sqref="I28">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I26))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I26">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I28))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2158,12 +2219,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I28">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I28))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I28">
+  <conditionalFormatting sqref="I29">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
